--- a/www/download/COUNTRY.SVK.EXI382.xlsx
+++ b/www/download/COUNTRY.SVK.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>Eslováquia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3948</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.047</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2.243</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2.321</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2.313</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2.249</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2.215</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2.179</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2.174</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2.195</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2.249</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2.224</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2.292</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2.344</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2.439</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2.382</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2.311</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2.314</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2.319</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2.284</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2.423</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2.353</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2.523</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2.546</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>2.621</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2.769</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2.597</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.095</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2.172</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2.165</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2.095</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.044</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.003</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1.988</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2.008</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.033</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1.956</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2.003</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.123</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.051</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.992</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>1.946</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.945</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>1.945</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2.036</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>1.976</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2.137</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2.154</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>2.225</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2.351</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>6331.051</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4908.361</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>5076.616</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>5064.473</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4925.064</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4863.195</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4718.968</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>4642.952</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>4664.118</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>4752.209</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>4718.144</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>4898.591</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>4898.066</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>5121.643</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>4948.559</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>4826.991</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>4754.817</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>4761.002</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>4770.787</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>4695.304</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>4760.553</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4994.777</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>4844.226</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>5195.624</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>5253.491</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>5422.07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>5742.24</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6233.695</t>
+          <t>16060048009.4891</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4769.835</t>
+          <t>5054956313.50061</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4935.474</t>
+          <t>6568321997.59501</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4921.569</t>
+          <t>6194025995.65292</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4781.274</t>
+          <t>5853039434.39017</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4724.386</t>
+          <t>6116243485.71758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4559.328</t>
+          <t>6180347473.97964</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4512.368</t>
+          <t>5949158289.67702</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4555.518</t>
+          <t>6043655877.8913</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4647.109</t>
+          <t>6167585443.3634</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4569.028</t>
+          <t>6255481659.53066</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4747.425</t>
+          <t>6765887508.30455</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4744.027</t>
+          <t>6761543800.24413</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>4950.275</t>
+          <t>7664091888.1906</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4792.477</t>
+          <t>7359501396.71916</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>4651.383</t>
+          <t>6535662820.55852</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>4562.405</t>
+          <t>6878857366.05226</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>4577.578</t>
+          <t>6918379956.57999</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>4608.85</t>
+          <t>7162283115.49403</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>4618.911</t>
+          <t>6862151434.37638</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>4683.65</t>
+          <t>7050180315.24271</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4915.401</t>
+          <t>7644199000.03888</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>4769.513</t>
+          <t>7106008491.03779</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5116.14</t>
+          <t>8231372234.97995</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>5172.893</t>
+          <t>8269975553.67228</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>5339.802</t>
+          <t>8835235033.41149</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>5654.551</t>
+          <t>8579413260.9146</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2562202478.72256</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1084308039.76699</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1880733417.92211</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1264627728.29253</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1185619553.53196</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1319949111.59143</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1272940253.06321</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1386386969.31732</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1492126922.51731</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1404066287.00131</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1448699982.94729</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1519055510.73564</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1816488671.5362</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1586819730.96065</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1639567228.54485</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1970880763.44668</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1981364040.26562</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2020843358.26342</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1912386165.98444</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2142529801.24004</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>1749077428.93577</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1771714391.89138</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1979003810.40649</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2110174303.6292</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2244815984.04624</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>2678451104.13125</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2279560685.52647</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>366968292.594568</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>372934834.017617</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>404402002.988532</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>293012830.385418</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>237133749.533776</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>69508642.1963751</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>237607446.128822</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>180757601.849001</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>45950753.4690675</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>50517942.6929715</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>265293186.248899</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>78350229.0167827</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2349161788.01491</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>32751413.8014672</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>53475750.0032452</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>39715021.6339071</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>43165094.6268412</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>46730950.0261177</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>47363914.2887824</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>43709820.6285791</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>30767931.8900268</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>36425745.2493165</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>28975068.9135118</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>32575105.9537996</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>30865804.3940928</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>28140277.8853752</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>19206133.1675748</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15581.5027193121</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>26306.2641068208</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>29572.6212790908</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>30234.7199555176</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>31244.1573604842</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>35574.4368627119</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>34117.5468033844</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>32795.7054425615</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>29938.2958834332</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>29355.9745140157</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>31296.2482279683</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>34381.6118077942</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>35933.1483728328</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>37172.8606240562</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>36626.7746596108</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>38891.3070510625</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>39761.9986382911</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>44228.8352487957</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>43490.113722287</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>44625.5053036445</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>52426.5781520979</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>50165.1610704164</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>51589.1955444206</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>54414.5826223858</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>58878.9463173784</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>57884.0959810489</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>59652.9467970158</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>59865.4773833746</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>38412.9791548937</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>54363.5316088376</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>52704.6018788137</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52532.7546718274</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>65620.0354923215</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>66579.3474098692</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>62124.8987473769</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>57975.4706075823</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>57817.547362605</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>62866.1630309541</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>72735.3874722796</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>75309.4808408174</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>85772.7573953338</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>82537.9054816699</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>84528.0783713168</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>92619.0733139964</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>102816.459849393</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>103974.715361883</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>103112.326395203</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>119670.79802673</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>118266.749133904</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>116233.625040004</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>130948.412286923</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>140175.016627635</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>142463.367551579</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>135817.77571583</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.4329437504159</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3.39896673737281</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.62422837440353</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2.89171365603776</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3.03272195178968</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2.57921828842562</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2.58172977013556</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2.25476804086086</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2.05303652876524</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2.30975043203027</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2.15388144804454</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2.12524787043508</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.61164689564933</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2.11962027154996</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.92301341266288</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.36005297036061</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.30265862672449</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.26518200002016</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.40999965486951</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.15582106569285</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1.6777832284631</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1.77437572452326</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1.41005753535284</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>1.42451073910044</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1.30437286145636</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.993615503268341</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1.48054419699883</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>986.556853494124</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>517.470668973385</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>866.018979565331</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>584.231603202794</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>565.901175854114</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>645.609739100845</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>635.453401089978</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>697.412832294169</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>743.202133046239</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>690.569686701224</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>740.757776217076</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>758.465903103644</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>886.135261006067</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>747.406966680854</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>799.282030198</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>989.298646444409</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1018.43435634309</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1039.1008629492</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>975.806799665455</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1107.74173689142</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>899.125220213734</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>870.404795023686</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1001.4046550403</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>987.393447347727</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1042.00242522114</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1203.68112691802</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>969.596403338078</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>4194968592.0957</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>-560842538.191389</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>728196265.857056</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>299204930.336654</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>317732179.377769</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>529464295.541061</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>428263890.029064</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>510692177.045826</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>925629045.154169</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1560920873.45855</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1264896975.55858</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1123382063.15149</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1319158110.33413</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>1432802874.14913</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1327396421.05074</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>1793067792.50625</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1843492186.2451</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>2180128620.78667</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>2221601512.70736</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>2204430199.3463</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>1656314443.10113</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1803877044.0053</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>1788066495.15281</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>2255357977.19961</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>2089028147.83464</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>2488593048.31405</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1882144488.86297</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>4027944280.37462</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-503876814.431138</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>669856738.703558</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>336884181.988857</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>330526605.715576</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>519403440.888819</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>408998917.974654</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>499861925.335446</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>804803084.987647</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1383234809.73442</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1136062107.37926</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>989179642.558146</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1107224774.85044</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>1392749661.02204</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1306508557.48157</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1707854667.29361</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1841041127.81965</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2133444053.68512</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2167525342.86148</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2214057901.45905</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>1761490137.55052</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>1886412387.69321</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>1827081218.46641</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>2339374909.43662</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2188618990.47039</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>2579389696.18604</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>3432599557.56048</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>167024311.721077</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-56965723.7602509</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>58339527.1534978</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-37679251.652203</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12794426.3378079</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>10060854.6522425</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>19264972.0544101</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>10830251.7103798</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>120825960.166522</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>177686063.724138</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>128834868.179317</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>134202420.593347</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>211933335.483694</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>40053213.1270964</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>20887863.5691703</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>85213125.2126476</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2451058.42544825</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>46684567.1015491</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>54076169.8458773</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-9627702.11274569</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-105175694.449391</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-82535343.6879087</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-39014723.3135946</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-84016932.2370071</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-99590842.6357533</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-90796647.8719961</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-1550455068.69751</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>2400.2373311385</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>2276.33626037997</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>2272.63157894733</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>2273.66210847315</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>2282.12209441048</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>2310.77818537543</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>2276.02236421786</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>2269.91699783731</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>2269.02326044641</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>2285.61331890638</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>2336.26220790577</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>2370.39394847229</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>2314.2724035319</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>2331.62592435526</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>2336.31209476917</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>2334.79720911486</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>2345.10665638601</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>2353.75257095793</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>2351.69405041307</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>2388.0929717377</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>2407.66243497653</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>2414.82993382236</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>2413.44283481727</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>2393.94601681197</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>2401.16211025131</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>2399.67735561526</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>2405.12673173121</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2078.12324272768</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>2188.00918290032</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2187.15953642664</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2189.3796472423</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>2189.79325063333</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2195.47424495499</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2165.75703336606</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2135.77073462475</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>2124.68932215665</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2112.75018894795</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>2121.46762589983</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>2137.34936079244</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>2089.44032079183</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>2099.80853593502</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>2077.82961034594</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>2045.16185069046</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2057.29361370699</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>2057.65493992506</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>2057.26045709359</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>2055.46119584681</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>2060.7440294273</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2061.25876734365</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>2059.09865976786</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>2059.00130752487</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>2063.69583543819</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>2068.58383743054</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>2073.57817563434</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3137.59846712882</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8663.82598142479</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>10882.9422169927</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>8933.28256223638</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>9112.74265807791</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>12710.3540759144</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>14393.0578652734</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>15442.2096964888</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>18966.1587779379</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>24551.3157792734</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>29265.8993860512</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>37812.6815613798</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>46730.0658796659</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>51240.5964526098</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>43969.5379215466</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>52863.7411965294</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>60492.3323292782</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>69386.7838599902</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>71710.1138978186</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>71284.4670605588</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>77686.9049638422</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>80914.7601758294</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>85364.5370887842</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>89052.2089094911</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>89897.2567903045</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>94227.8980552842</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>96318.1777397611</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1146776841.61498</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1220139811.46928</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1721501505.69282</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1254560938.89351</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1291252180.60275</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1511567715.90862</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1493471639.3391</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1552357051.19088</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1597455061.88322</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1904634808.668</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1979365968.99898</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2399433901.33775</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2396152201.94908</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2758249184.13134</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2647337361.68274</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2322273922.76105</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2543315149.29417</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2773992747.35282</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>3008681367.33706</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2678230811.5095</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2902708832.29075</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>3378487035.8143</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>3195465716.8631</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>3669164188.99825</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>3730283238.755</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>3989891877.62045</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3760629210.16935</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3277.73483655728</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>11615.5632526566</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>13504.4797870933</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>11871.5708845984</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>10336.1629458578</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>13407.972231034</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>16720.4077624052</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>17649.9395009894</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>19154.3643766188</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>25257.7006137347</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>30876.4370494253</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>39091.2109242059</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>46412.2377346766</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>52767.4427303638</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>44110.1974444429</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>53139.6833310522</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>59836.2819422965</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>64081.5827545917</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>66261.9508184754</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>66485.2655504335</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>74480.2771142795</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>77790.8072198783</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>82921.2143014138</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>86838.8234305913</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>89412.9966331408</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>93220.0298276746</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>94757.4946052453</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6331.051</t>
+          <t>5421136364.12797</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4908.361</t>
+          <t>1258907423.17605</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5076.616</t>
+          <t>2940417404.81597</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5064.473</t>
+          <t>2107334454.3858</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4925.064</t>
+          <t>1833413340.1702</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4863.195</t>
+          <t>2149260895.524</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4718.968</t>
+          <t>2297088166.79848</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4642.952</t>
+          <t>2432476495.51613</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4664.118</t>
+          <t>2555056033.19318</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>4752.209</t>
+          <t>3595099485.06213</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>4718.144</t>
+          <t>3513626309.82096</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4898.591</t>
+          <t>3713050521.3651</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4898.066</t>
+          <t>3675841649.17385</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>5121.643</t>
+          <t>4400290078.88969</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>4948.559</t>
+          <t>3995437656.23633</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>4826.991</t>
+          <t>4149365936.85947</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>4754.817</t>
+          <t>4311154389.64504</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>4761.002</t>
+          <t>4375688758.02425</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>4770.787</t>
+          <t>4606176421.23525</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>4695.304</t>
+          <t>4372476650.99485</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>4760.553</t>
+          <t>4249054968.1996</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>4994.777</t>
+          <t>4851048463.98934</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>4844.226</t>
+          <t>4748184624.83912</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>5195.624</t>
+          <t>5704534433.84249</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>5253.491</t>
+          <t>5775114218.16891</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>5422.07</t>
+          <t>6380680056.26347</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>5742.24</t>
+          <t>5490708422.3522</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6233.695</t>
+          <t>-140.136369428463</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4769.835</t>
+          <t>-2951.73727123177</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4935.474</t>
+          <t>-2621.53757010053</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4921.569</t>
+          <t>-2938.28832236201</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4781.274</t>
+          <t>-1223.42028777989</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4724.386</t>
+          <t>-697.618155119611</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4559.328</t>
+          <t>-2327.34989713185</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4512.368</t>
+          <t>-2207.72980450068</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4555.518</t>
+          <t>-188.205598680889</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4647.109</t>
+          <t>-706.384834461221</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>4569.028</t>
+          <t>-1610.5376633741</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>4747.425</t>
+          <t>-1278.52936282613</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>4744.027</t>
+          <t>317.828144989278</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>4950.275</t>
+          <t>-1526.846277754</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>4792.477</t>
+          <t>-140.65952289638</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>4651.383</t>
+          <t>-275.942134522788</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>4562.405</t>
+          <t>656.050386981669</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>4577.578</t>
+          <t>5305.20110539845</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>4608.85</t>
+          <t>5448.16307934321</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>4618.911</t>
+          <t>4799.20151012524</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>4683.65</t>
+          <t>3206.62784956266</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>4915.401</t>
+          <t>3123.95295595102</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>4769.513</t>
+          <t>2443.32278737032</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>5116.14</t>
+          <t>2213.38547889982</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>5172.893</t>
+          <t>484.260157163672</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>5339.802</t>
+          <t>1007.86822760956</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>5654.551</t>
+          <t>1560.68313451578</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>15694.668</t>
+          <t>-4274359522.51299</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5336.336</t>
+          <t>-38767611.7067761</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6697.986</t>
+          <t>-1218915899.12315</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>6412.594</t>
+          <t>-852773515.492298</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6090.89</t>
+          <t>-542161159.567453</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6260.341</t>
+          <t>-637693179.615387</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6313.073</t>
+          <t>-803616527.45938</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6104.722</t>
+          <t>-880119444.325242</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6192.551</t>
+          <t>-957600971.309958</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>6204.186</t>
+          <t>-1690464676.39413</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>6268.942</t>
+          <t>-1534260340.82198</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>6696.171</t>
+          <t>-1313616620.02735</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>6729.945</t>
+          <t>-1279689447.22477</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>7536.595</t>
+          <t>-1642040894.75835</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>7337.11</t>
+          <t>-1348100294.55359</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>6537.737</t>
+          <t>-1827092014.09843</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>6726.674</t>
+          <t>-1767839240.35087</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>6792.766</t>
+          <t>-1601696010.67143</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>6998.271</t>
+          <t>-1597495053.89819</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>6748.617</t>
+          <t>-1694245839.48535</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>6928.145</t>
+          <t>-1346346135.90885</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>7466.637</t>
+          <t>-1472561428.17504</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>6966.74</t>
+          <t>-1552718907.97603</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>7976.791</t>
+          <t>-2035370244.84424</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>8080.162</t>
+          <t>-2044830979.41391</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>8552.185</t>
+          <t>-2390788178.64302</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>8469.908</t>
+          <t>-1730079212.18284</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>7189.19401818466</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>7137.15055920031</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>8696.58480529355</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>8899.29201256107</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>7796.124014526</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>10017.519176206</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>9537.2740843057</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>10659.3814073699</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>13057.7644597535</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>13308.6832389912</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>15714.877026421</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>17742.3602071147</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>21058.1129308912</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>23173.4648705924</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>22413.897100753</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>24732.5140705463</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>25835.6336024795</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>26703.3825279265</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>25180.6324169219</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>27840.8843231896</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>28173.8253866987</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>26298.5982817292</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>28829.0913980871</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>27940.8077591805</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>29873.3504203053</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>33306.9340468619</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>36206.2278466417</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>4180.033</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>3461.773</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>3573.029</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>3553.288</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>3481.129</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>3315.785</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3167.023</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>3140.558</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>3120.919</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>3131.497</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>3114.125</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>3198.197</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>3226.201</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>3321.523</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>3265.83</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>3007.054</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>2953.14</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2976.098</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>2995.81</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>2969.839</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>3088.613</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>3242.437</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>3153.935</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>3420.482</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>3473.711</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>3589.832</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>3768.191</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>9375.05576285781</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>10611.2456508434</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>13239.6470547154</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>12567.5987021158</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>11538.1308570934</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>14088.7214315674</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>13682.874407064</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>15773.3391264996</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>18091.6239490678</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>19014.7298867996</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>23245.5081308663</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>25223.5471582575</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>33333.2824475445</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>34933.3272598544</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>35924.7986100508</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>40003.1817466212</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>41229.1909904213</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>43346.219257629</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>40866.9084923473</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>45220.6360521956</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45241.9829005957</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>41979.9500643039</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>49075.8540340394</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46784.0404246312</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48590.5103729998</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>54398.1627670496</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>58325.2977733658</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2284.795</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>960.696</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1643.639</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1138.222</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>1070.468</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>1199.492</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1140.997</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>1214.622</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>1317.055</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1207.863</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>1231.139</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>1273.087</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1546.228</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>1342.82</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>1396.925</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1663.622</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>1652.535</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>1652.264</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>1572.779</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>1789.073</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>1446.603</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>1462.745</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>1623.231</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>1702.026</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>1820.07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>2154.845</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1844.55</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>172.83</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>396.5</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>200.28</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>332.39</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>346.65</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>293.87</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>299.59</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>271.5</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>245.89</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>284.74</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>271.12</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>272.91</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>206.81</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>268.65</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>243.07</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>179.59</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>176.09</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>177.05</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>193.04</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>158.17</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>223.77</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>236.04</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>193.83</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>200.59</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>184.21</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>147.8</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>206.55</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>504.006</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>520.16</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>562.234</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>407.893</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>329.837</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>95.881</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>330.27</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>251.201</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>63.242</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>69.497</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>369.165</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>108.623</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>3276.001</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>44.886</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>73.907</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>54.816</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>59.478</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>64.488</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>65.266</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>60.515</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>42.51</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>50.283</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>39.939</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>44.993</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>42.641</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>38.768</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>26.374</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>10802.5690001695</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>12066.8860578023</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>12794.9791013041</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>14435.9974435489</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>14596.0179017656</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>15525.0461284624</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>18196.3055063577</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>19338.8023112044</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>21674.9359715523</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>27207.0327438389</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>28919.7749699678</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>35410.9805546333</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>42402.3728641776</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>53215.8779955582</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>49851.6208808733</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>51666.5308777905</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>54348.5049643392</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>55522.8354185306</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>59104.197151357</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>56958.0927342465</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>61546.5417680535</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>66529.3094029038</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>64097.7855255149</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>74311.05512184</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>77493.7008887618</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>74432.4045101388</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>73773.988550157</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>6233694507.90817</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4769835000.00089</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>4935474000.00013</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4921569000.00004</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>4781273999.9994</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>4724385999.9992</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4559328000.0004</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>4512367999.99995</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>4555517999.9994</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>4647109000.00173</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>4569027999.99989</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>4747424999.99924</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>4744026999.99968</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>4950275000.00029</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>4792476999.99911</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>4651382999.99893</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>4562404999.99933</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>4577577999.99858</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>4608849999.99972</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>4618910879.38799</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>4683650204.48756</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>4915401399.65194</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>4769513045.76214</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>5116140260.5228</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>5172893032.59962</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>5339801645.94227</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>5654551030.18936</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>6331050955.80502</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4908361000.0008</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>5076616000.00021</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>5064473000.00012</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>4925063999.99941</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>4863194999.9992</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4718968000.00049</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>4642951999.99997</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>4664117999.99938</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>4752209000.00168</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>4718143999.99992</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>4898590999.99925</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>4898065999.99966</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>5121643000.00025</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>4948558999.99906</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>4826990999.99898</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>4754816999.99936</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>4761001999.9986</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>4770786999.99976</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>4695304433.36828</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>4760553339.33451</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>4994776697.6024</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>4844226311.65836</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>5195623690.75272</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>5253490749.89922</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>5422069675.11295</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>5742240345.23911</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>4180033178.88235</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3461773045.38608</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3573029439.50796</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3553288227.20968</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3481128797.97789</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3315784822.22999</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3167022543.89208</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3140557921.75691</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3120919174.84661</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3131497086.04714</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3114125268.08388</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3198197272.74274</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>3226201454.19852</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>3321523385.99257</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3265830380.49817</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>3007053684.81211</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2953140292.11557</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2976098260.3016</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2995810145.95636</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2969838679.18455</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>3088613390.88668</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>3242436922.46152</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>3153934685.0646</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>3420481980.29706</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>3473710639.63694</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>3589832259.88925</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>3768190725.44494</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3046523.33684265</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2243300.00000024</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2321100.00000015</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2313199.99999966</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2249099.99999999</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2215099.99999973</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2178899.99999962</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2173899.99999963</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2195200.00000052</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2249300.0000005</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2223999.99999938</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2291899.99999956</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2344199.99999974</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2439100.00000055</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2381599.9999996</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2360199.99999969</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2311199.99999988</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2313799.99999999</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2318999.99999986</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2284307.01725503</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>2310113.8575942</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>2423168.20029307</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2352595.53430261</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>2523370.75832088</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2545671.05272261</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>2621150.55575794</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2769242.27536417</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2597115.88809901</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2095400.00000031</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2171700.00000009</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2164599.99999959</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2095100</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2044499.99999962</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2003199.99999964</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1987899.99999963</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2007700.0000005</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2033200.00000056</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1955699.9999994</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2002799.99999956</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2049899.99999984</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2123100.0000007</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2051299.99999962</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1992200.00000013</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1945500.00000014</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1944799.99999983</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1959800.00000008</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1934141.98444168</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>1945310.16327179</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>2035506.24033864</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>1976227.89193731</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>2137115.96861152</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2154328.94368728</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>2225216.49981282</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2351040.78117298</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6331050955.80502</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4908361000.0008</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5076616000.00021</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5064473000.00012</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>4925063999.99941</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>4863194999.9992</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4718968000.00049</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>4642951999.99997</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>4664117999.99938</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>4752209000.00168</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>4718143999.99992</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>4898590999.99925</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>4898065999.99966</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>5121643000.00025</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>4948558999.99906</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>4826990999.99898</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>4754816999.99936</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>4761001999.9986</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>4770786999.99976</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>4695304433.36828</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>4760553339.33451</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>4994776697.6024</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>4844226311.65836</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>5195623690.75272</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>5253490749.89922</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>5422069675.11295</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>5742240345.23911</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6233694507.90817</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4769835000.00089</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4935474000.00013</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4921569000.00004</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>4781273999.9994</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4724385999.9992</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4559328000.0004</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>4512367999.99995</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>4555517999.9994</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4647109000.00173</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>4569027999.99989</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4747424999.99924</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4744026999.99968</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>4950275000.00029</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4792476999.99911</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>4651382999.99893</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>4562404999.99933</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>4577577999.99858</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>4608849999.99972</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>4618910879.38799</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>4683650204.48756</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>4915401399.65194</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>4769513045.76214</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>5116140260.5228</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>5172893032.59962</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>5339801645.94227</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>5654551030.18936</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>43114.3391896904</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>48041.1787225426</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>56925.6003602804</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>58868.1344733404</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>55241.0882717346</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>66811.4476228073</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>72685.9916257916</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>79646.6314364474</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>90479.6642357113</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>102343.079778927</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>118808.628422212</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>144496.486334708</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>176070.580120211</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>204786.36094557</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>189127.132995572</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>207890.572511841</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>222661.212959426</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>235320.222644822</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>236371.601240104</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>240697.962959426</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>254380.843208968</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>253155.034249271</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>268040.625196381</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>284680.477583729</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>291009.633855873</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>307532.768574081</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>310797.83436011</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>10569.6432488979</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>11720.1010040471</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>14162.5178340331</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>13954.6219281486</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>12648.7755471314</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>15764.9358632358</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15148.0598365067</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>17258.0336410922</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>20225.5855192421</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>21149.3629405559</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>26053.1570507822</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>28102.7808711236</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>36020.4072061507</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>38518.8805085469</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>39189.3046603139</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>43351.4897552323</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>44973.6828581277</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>47105.6222038905</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>44708.8329219687</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>49281.5877529581</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>49669.8133954904</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>46444.8962582173</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>53805.7498910131</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>50526.4159257202</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>53426.4669665078</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>60022.6078772311</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>64377.1921277625</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
